--- a/data/trans_orig/Q25B01-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q25B01-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de cigarrillos que fumaban antes de haber dejado de fumar</t>
+          <t>Número medio de cigarrillos que fumaban antes de haber dejado de fumar (tasa de respuesta: 96,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,71; 26,69</t>
+          <t>20,8; 26,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,65; 25,21</t>
+          <t>19,78; 25,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,8; 21,71</t>
+          <t>15,52; 21,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,59; 22,89</t>
+          <t>17,78; 22,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,68; 15,57</t>
+          <t>11,72; 15,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,46; 14,91</t>
+          <t>9,45; 15,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,6; 13,49</t>
+          <t>9,55; 13,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,15; 14,16</t>
+          <t>9,97; 14,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,65; 23,53</t>
+          <t>18,65; 23,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,78; 21,22</t>
+          <t>16,99; 21,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,6; 18,04</t>
+          <t>13,62; 17,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,43; 19,16</t>
+          <t>15,64; 19,3</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,85; 23,11</t>
+          <t>18,2; 23,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,53; 23,93</t>
+          <t>17,64; 24,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,67; 23,74</t>
+          <t>17,51; 23,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,37; 19,97</t>
+          <t>15,41; 19,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,58; 12,43</t>
+          <t>8,49; 12,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,09; 16,7</t>
+          <t>12,05; 16,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,6; 17,1</t>
+          <t>12,65; 16,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,86; 14,28</t>
+          <t>9,79; 14,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,15; 19,2</t>
+          <t>15,16; 19,26</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,2; 20,73</t>
+          <t>16,12; 20,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,99; 19,93</t>
+          <t>15,93; 19,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,59; 17,01</t>
+          <t>13,83; 17,14</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,17; 24,31</t>
+          <t>19,11; 24,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,16; 29,38</t>
+          <t>23,0; 29,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,74; 24,24</t>
+          <t>19,03; 24,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,48; 23,88</t>
+          <t>19,06; 23,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,22; 19,39</t>
+          <t>11,47; 19,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,51; 16,04</t>
+          <t>10,7; 16,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,33; 14,94</t>
+          <t>8,3; 14,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,17; 15,87</t>
+          <t>9,4; 15,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,22; 22,76</t>
+          <t>18,02; 22,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,24; 27,0</t>
+          <t>21,37; 26,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,74; 22,34</t>
+          <t>17,9; 22,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,76; 22,28</t>
+          <t>18,67; 22,11</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,51; 24,3</t>
+          <t>21,45; 24,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,17; 24,33</t>
+          <t>21,22; 24,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,29; 26,23</t>
+          <t>22,38; 26,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,22; 23,85</t>
+          <t>20,23; 23,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,94; 16,2</t>
+          <t>11,09; 16,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,42; 18,76</t>
+          <t>13,41; 18,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,93; 15,99</t>
+          <t>11,96; 16,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,75; 13,77</t>
+          <t>10,7; 13,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,83; 22,38</t>
+          <t>19,73; 22,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,6; 22,31</t>
+          <t>19,58; 22,39</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19,56; 22,9</t>
+          <t>19,54; 22,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,8; 20,67</t>
+          <t>17,66; 20,5</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,24; 26,84</t>
+          <t>19,99; 27,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,05; 26,16</t>
+          <t>20,84; 26,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,18; 24,74</t>
+          <t>19,01; 24,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,2; 23,9</t>
+          <t>18,33; 24,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,23; 18,04</t>
+          <t>10,33; 18,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,5; 14,0</t>
+          <t>10,5; 14,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,96; 13,88</t>
+          <t>9,87; 13,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,93; 15,64</t>
+          <t>12,0; 15,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,13; 22,45</t>
+          <t>17,15; 22,6</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,72; 21,6</t>
+          <t>17,75; 21,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,94; 20,08</t>
+          <t>15,99; 19,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,97; 19,84</t>
+          <t>15,87; 19,6</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,54; 17,54</t>
+          <t>7,25; 17,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,96; 29,64</t>
+          <t>9,0; 29,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1431,47 +1431,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,1; 24,37</t>
+          <t>8,62; 24,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,06; 12,98</t>
+          <t>9,13; 12,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,81; 13,69</t>
+          <t>8,92; 14,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,12; 21,92</t>
+          <t>13,22; 21,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,92; 14,58</t>
+          <t>9,11; 14,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,38; 13,08</t>
+          <t>9,4; 12,98</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,62; 14,59</t>
+          <t>9,78; 14,51</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,93; 20,72</t>
+          <t>12,91; 20,4</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,79; 14,74</t>
+          <t>9,72; 14,81</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,38; 23,42</t>
+          <t>21,34; 23,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22,11; 24,47</t>
+          <t>22,08; 24,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,54; 22,83</t>
+          <t>20,51; 22,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,83; 21,59</t>
+          <t>19,78; 21,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,56; 13,83</t>
+          <t>11,64; 13,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,26; 14,42</t>
+          <t>12,39; 14,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,32; 14,34</t>
+          <t>12,33; 14,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,49; 13,22</t>
+          <t>11,54; 13,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,76; 20,4</t>
+          <t>18,8; 20,48</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,22; 21,03</t>
+          <t>19,17; 20,89</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,86; 19,65</t>
+          <t>17,78; 19,56</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,31; 19,15</t>
+          <t>17,36; 19,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q25B01-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q25B01-Clase-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20,25</t>
+          <t>20,29</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,8</t>
+          <t>11,92</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,34</t>
+          <t>17,39</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,8; 26,94</t>
+          <t>20,87; 27,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,78; 25,47</t>
+          <t>19,69; 25,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,52; 21,81</t>
+          <t>15,43; 21,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,78; 22,64</t>
+          <t>17,86; 22,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,72; 15,63</t>
+          <t>11,7; 15,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,45; 15,19</t>
+          <t>9,47; 15,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,55; 13,64</t>
+          <t>9,55; 13,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,97; 14,15</t>
+          <t>10,27; 14,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,65; 23,73</t>
+          <t>18,63; 23,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,99; 21,46</t>
+          <t>16,58; 21,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,62; 17,73</t>
+          <t>13,72; 17,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,64; 19,3</t>
+          <t>15,68; 19,08</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,38</t>
+          <t>17,14</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,87</t>
+          <t>12,13</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,28</t>
+          <t>15,22</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,2; 23,49</t>
+          <t>18,07; 23,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,64; 24,14</t>
+          <t>17,74; 24,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,51; 23,81</t>
+          <t>17,79; 23,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,41; 19,86</t>
+          <t>15,24; 19,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,49; 12,46</t>
+          <t>8,33; 12,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,05; 16,82</t>
+          <t>12,28; 16,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,65; 16,95</t>
+          <t>12,71; 16,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,79; 14,44</t>
+          <t>10,13; 14,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,16; 19,26</t>
+          <t>15,16; 19,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,12; 20,64</t>
+          <t>16,11; 20,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,93; 19,85</t>
+          <t>15,92; 19,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,83; 17,14</t>
+          <t>13,71; 17,07</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,76</t>
+          <t>22,34</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,24</t>
+          <t>12,18</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,24</t>
+          <t>20,53</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,11; 24,39</t>
+          <t>19,08; 24,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,0; 29,5</t>
+          <t>23,27; 29,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,03; 24,29</t>
+          <t>18,59; 24,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,06; 23,74</t>
+          <t>20,01; 25,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,47; 19,52</t>
+          <t>11,28; 19,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,7; 16,07</t>
+          <t>10,64; 16,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,3; 14,86</t>
+          <t>8,43; 14,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,4; 15,97</t>
+          <t>9,62; 15,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,02; 22,57</t>
+          <t>18,08; 22,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,37; 26,98</t>
+          <t>21,46; 27,57</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,9; 22,85</t>
+          <t>17,62; 22,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,67; 22,11</t>
+          <t>18,43; 22,69</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,94</t>
+          <t>21,32</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,16</t>
+          <t>12,12</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,05</t>
+          <t>18,66</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,45; 24,15</t>
+          <t>21,49; 24,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,22; 24,48</t>
+          <t>21,25; 24,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,38; 26,2</t>
+          <t>22,21; 26,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,23; 23,83</t>
+          <t>19,5; 23,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,09; 16,24</t>
+          <t>11,11; 16,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,41; 18,68</t>
+          <t>13,3; 18,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,96; 16,24</t>
+          <t>11,91; 16,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,7; 13,7</t>
+          <t>10,59; 13,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,73; 22,26</t>
+          <t>19,76; 22,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,58; 22,39</t>
+          <t>19,62; 22,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19,54; 22,76</t>
+          <t>19,69; 22,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,66; 20,5</t>
+          <t>17,37; 20,13</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21,0</t>
+          <t>21,76</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,69</t>
+          <t>13,47</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,74</t>
+          <t>17,95</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1276,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,99; 27,03</t>
+          <t>20,36; 27,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,84; 26,1</t>
+          <t>20,8; 26,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,01; 24,06</t>
+          <t>18,8; 24,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,33; 24,15</t>
+          <t>19,22; 24,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,33; 18,48</t>
+          <t>10,28; 17,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,5; 14,03</t>
+          <t>10,65; 14,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,87; 13,66</t>
+          <t>9,85; 13,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,0; 15,91</t>
+          <t>11,78; 15,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,15; 22,6</t>
+          <t>17,03; 22,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,75; 21,66</t>
+          <t>17,83; 21,65</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,99; 19,83</t>
+          <t>15,87; 19,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,87; 19,6</t>
+          <t>16,27; 20,03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15,6</t>
+          <t>15,94</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11,78</t>
+          <t>12,25</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,39</t>
+          <t>12,81</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,25; 17,1</t>
+          <t>7,25; 17,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,0; 29,62</t>
+          <t>8,88; 29,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,06; 18,14</t>
+          <t>5,23; 18,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,62; 24,3</t>
+          <t>8,76; 24,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,13; 12,87</t>
+          <t>9,15; 13,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,92; 14,01</t>
+          <t>8,93; 13,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,22; 21,25</t>
+          <t>13,08; 21,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,11; 14,25</t>
+          <t>9,95; 14,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,4; 12,98</t>
+          <t>9,48; 13,25</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,78; 14,51</t>
+          <t>9,69; 14,76</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,91; 20,4</t>
+          <t>13,16; 20,78</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,72; 14,81</t>
+          <t>10,44; 14,93</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20,56</t>
+          <t>20,63</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>12,33</t>
+          <t>12,4</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,24</t>
+          <t>17,7</t>
         </is>
       </c>
     </row>
@@ -1556,27 +1556,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,34; 23,48</t>
+          <t>21,31; 23,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22,08; 24,29</t>
+          <t>22,06; 24,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,51; 22,81</t>
+          <t>20,49; 22,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,78; 21,53</t>
+          <t>19,69; 21,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,64; 13,87</t>
+          <t>11,5; 13,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,33; 14,36</t>
+          <t>12,35; 14,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,54; 13,17</t>
+          <t>11,59; 13,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,8; 20,48</t>
+          <t>18,78; 20,45</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,17; 20,89</t>
+          <t>19,28; 21,0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,78; 19,56</t>
+          <t>17,83; 19,6</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,36; 19,18</t>
+          <t>16,93; 18,5</t>
         </is>
       </c>
     </row>
